--- a/models/Comps_Precs.xlsx
+++ b/models/Comps_Precs.xlsx
@@ -431,7 +431,7 @@
     <numFmt numFmtId="164" formatCode="0.00;[Red]0.00;\-"/>
     <numFmt numFmtId="165" formatCode="0;\(0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.00;\(0.00\);\-"/>
-    <numFmt numFmtId="168" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00&quot;x&quot;"/>
   </numFmts>
   <fonts count="15" x14ac:knownFonts="1">
     <font>
@@ -697,14 +697,14 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2686,7 +2686,7 @@
         <v>-13.839211777752116</v>
       </c>
       <c r="I31" s="29">
-        <f t="shared" ref="G31:I31" si="10">I28-$K$30</f>
+        <f t="shared" ref="I31" si="10">I28-$K$30</f>
         <v>0</v>
       </c>
     </row>

--- a/models/Comps_Precs.xlsx
+++ b/models/Comps_Precs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cb10f4a09bcef627/Documents/GitHub/XD_Grad_Portfolio/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="814" documentId="8_{03E98026-E5C0-4EE9-B1A4-ED0B6BC034C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4433886C-081E-4B0B-8D7E-757F4A247425}"/>
+  <xr:revisionPtr revIDLastSave="815" documentId="8_{03E98026-E5C0-4EE9-B1A4-ED0B6BC034C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF65EFDF-1570-4236-9F0E-1DB56C48497E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{6F36A4A9-635C-494E-BE77-27E5FD1262DF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6F36A4A9-635C-494E-BE77-27E5FD1262DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Comparable Companies" sheetId="1" r:id="rId1"/>

--- a/models/Comps_Precs.xlsx
+++ b/models/Comps_Precs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cb10f4a09bcef627/Documents/GitHub/XD_Grad_Portfolio/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="815" documentId="8_{03E98026-E5C0-4EE9-B1A4-ED0B6BC034C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF65EFDF-1570-4236-9F0E-1DB56C48497E}"/>
+  <xr:revisionPtr revIDLastSave="817" documentId="8_{03E98026-E5C0-4EE9-B1A4-ED0B6BC034C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B70DF7FB-2AB4-4DCF-B0A4-2479D73E88E2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6F36A4A9-635C-494E-BE77-27E5FD1262DF}"/>
   </bookViews>
@@ -91,6 +91,30 @@
           </rPr>
           <t xml:space="preserve">
 All Comparables taken from peers stated by S&amp;N on the investors page of their website: https://www.smith-nephew.com/en/who-we-are/investors/shareholder-resources#sharepricechart</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{A3E3E905-BE62-4CCB-AC3F-3829AA374CBB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Xavier Davis:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+for some reason these values are rendering as 0.00 in the viewer, not really sure why. Fixes have been attempted to no avail</t>
         </r>
       </text>
     </comment>
